--- a/docs/StructureDefinition-BRCondicaoMaternal.xlsx
+++ b/docs/StructureDefinition-BRCondicaoMaternal.xlsx
@@ -1435,7 +1435,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2699,12 +2699,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK17">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
